--- a/Test upload format/MSME/MSME_Continuity.xlsx
+++ b/Test upload format/MSME/MSME_Continuity.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12180"/>
+    <workbookView windowWidth="24000" windowHeight="9600"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$21</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="51">
   <si>
     <t>CGPAN</t>
   </si>
@@ -56,37 +56,133 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN0605202600504017</t>
-  </si>
-  <si>
-    <t>loan01</t>
+    <t>CGMSMGEN2109202600357114</t>
+  </si>
+  <si>
+    <t>QAMSME20</t>
   </si>
   <si>
     <t>Standard</t>
   </si>
   <si>
-    <t>CGMSMGEN0605202600504018</t>
-  </si>
-  <si>
-    <t>loan02</t>
+    <t>CGMSMGEN2109202600357115</t>
+  </si>
+  <si>
+    <t>QAMSME19</t>
   </si>
   <si>
     <t>NPA</t>
   </si>
   <si>
-    <t>28-02-2027</t>
-  </si>
-  <si>
-    <t>CGMSMGEN0605202600504019</t>
-  </si>
-  <si>
-    <t>loan03</t>
-  </si>
-  <si>
-    <t>CGMSMGEN0605202600504020</t>
-  </si>
-  <si>
-    <t>loan04</t>
+    <t>30-11-2028</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357116</t>
+  </si>
+  <si>
+    <t>QAMSME18</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357117</t>
+  </si>
+  <si>
+    <t>QAMSME17</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357118</t>
+  </si>
+  <si>
+    <t>QAMSME16</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357119</t>
+  </si>
+  <si>
+    <t>QAMSME15</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357120</t>
+  </si>
+  <si>
+    <t>QAMSME14</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357121</t>
+  </si>
+  <si>
+    <t>QAMSME13</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357122</t>
+  </si>
+  <si>
+    <t>QAMSME12</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357123</t>
+  </si>
+  <si>
+    <t>QAMSME11</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357124</t>
+  </si>
+  <si>
+    <t>QAMSME10</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357125</t>
+  </si>
+  <si>
+    <t>QAMSME09</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357126</t>
+  </si>
+  <si>
+    <t>QAMSME08</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357127</t>
+  </si>
+  <si>
+    <t>QAMSME07</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357128</t>
+  </si>
+  <si>
+    <t>QAMSME06</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357129</t>
+  </si>
+  <si>
+    <t>QAMSME05</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357130</t>
+  </si>
+  <si>
+    <t>QAMSME04</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357131</t>
+  </si>
+  <si>
+    <t>QAMSME03</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357132</t>
+  </si>
+  <si>
+    <t>QAMSME02</t>
+  </si>
+  <si>
+    <t>CGMSMGEN2109202600357133</t>
+  </si>
+  <si>
+    <t>QAMSME01</t>
   </si>
 </sst>
 </file>
@@ -473,12 +569,38 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -603,7 +725,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -615,34 +737,34 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -728,7 +850,7 @@
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -745,7 +867,8 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1009,11 +1132,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr>
+  <sheetPr codeName="Sheet1">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
-  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelRow="4" outlineLevelCol="7"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="33.4285714285714" style="3" customWidth="1"/>
     <col min="2" max="2" width="22.7809523809524" style="3" customWidth="1"/>
@@ -1059,16 +1182,16 @@
       <c r="B2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6">
-        <v>10000000.79</v>
-      </c>
-      <c r="D2" s="6">
-        <v>10000000.79</v>
+      <c r="C2" s="7">
+        <v>180000000</v>
+      </c>
+      <c r="D2" s="7">
+        <v>180000000</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="7"/>
+      <c r="F2" s="8"/>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:8">
       <c r="A3" s="6" t="s">
@@ -1077,16 +1200,16 @@
       <c r="B3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="6">
-        <v>10000000.02</v>
-      </c>
-      <c r="D3" s="6">
-        <v>10000000.02</v>
+      <c r="C3" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="D3" s="7">
+        <v>100000000</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>14</v>
       </c>
       <c r="G3" s="2">
@@ -1103,16 +1226,16 @@
       <c r="B4" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="6">
-        <v>2000000.33</v>
-      </c>
-      <c r="D4" s="6">
-        <v>2000000.33</v>
+      <c r="C4" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D4" s="7">
+        <v>1000000000</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="7"/>
+      <c r="F4" s="8"/>
     </row>
     <row r="5" s="2" customFormat="1" ht="15" spans="1:8">
       <c r="A5" s="6" t="s">
@@ -1121,19 +1244,435 @@
       <c r="B5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="6">
-        <v>2000000.65</v>
-      </c>
-      <c r="D5" s="6">
-        <v>2000000.65</v>
+      <c r="C5" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D5" s="7">
+        <v>1000000000</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="7"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" ht="15" spans="1:8">
+      <c r="A6" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="D6" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" ht="15" spans="1:8">
+      <c r="A7" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="D7" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H7" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" ht="15" spans="1:8">
+      <c r="A8" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D8" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" ht="15" spans="1:8">
+      <c r="A9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D9" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G9" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" ht="15" spans="1:8">
+      <c r="A10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="D10" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G10" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H10" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" ht="15" spans="1:8">
+      <c r="A11" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="D11" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G11" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H11" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" ht="15" spans="1:8">
+      <c r="A12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D12" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H12" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" ht="15" spans="1:8">
+      <c r="A13" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H13" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" ht="15" spans="1:8">
+      <c r="A14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="7">
+        <v>150000000</v>
+      </c>
+      <c r="D14" s="7">
+        <v>150000000</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H14" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" ht="15" spans="1:8">
+      <c r="A15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="7">
+        <v>180000000</v>
+      </c>
+      <c r="D15" s="7">
+        <v>180000000</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H15" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" ht="15" spans="1:8">
+      <c r="A16" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D16" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H16" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" ht="15" spans="1:8">
+      <c r="A17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D17" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F17" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G17" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H17" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" ht="15" spans="1:8">
+      <c r="A18" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C18" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="D18" s="7">
+        <v>100000000</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G18" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H18" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" ht="15" spans="1:8">
+      <c r="A19" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="D19" s="7">
+        <v>200000000</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F19" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G19" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H19" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" ht="15" spans="1:8">
+      <c r="A20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D20" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F20" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G20" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H20" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" ht="15" spans="1:8">
+      <c r="A21" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="D21" s="7">
+        <v>1000000000</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F21" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="G21" s="2">
+        <v>10000</v>
+      </c>
+      <c r="H21" s="2">
+        <v>100</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H5" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H21" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
